--- a/data/trans_dic/P6903-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P6903-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que se siente agotado a todas horas</t>
+          <t>Población que su trabajo le afecta de manera que se siente agotado a todas horas (tasa de respuesta: 99,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24,81; 55,74</t>
+          <t>25,67; 58,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,99; 49,32</t>
+          <t>15,97; 46,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28,15; 56,5</t>
+          <t>29,07; 56,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,76; 39,9</t>
+          <t>6,11; 43,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,35; 59,39</t>
+          <t>21,12; 59,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,21; 76,16</t>
+          <t>38,94; 76,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,95; 63,69</t>
+          <t>33,1; 64,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,88; 51,01</t>
+          <t>12,79; 52,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28,18; 52,68</t>
+          <t>27,98; 51,96</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30,73; 55,22</t>
+          <t>30,93; 54,96</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35,6; 55,32</t>
+          <t>33,97; 56,09</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,15; 36,68</t>
+          <t>11,75; 39,27</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,7; 44,04</t>
+          <t>18,75; 42,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,85; 46,1</t>
+          <t>20,75; 45,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,03; 51,93</t>
+          <t>31,15; 53,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24,03; 60,92</t>
+          <t>23,55; 62,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,8; 45,09</t>
+          <t>15,35; 47,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,68; 42,28</t>
+          <t>11,03; 41,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,21; 74,56</t>
+          <t>44,19; 74,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>32,62; 57,65</t>
+          <t>31,82; 57,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,5; 40,42</t>
+          <t>22,14; 41,44</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20,03; 40,61</t>
+          <t>19,6; 40,89</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39,48; 57,26</t>
+          <t>39,08; 56,81</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>32,6; 55,13</t>
+          <t>31,77; 54,62</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,77; 52,19</t>
+          <t>19,56; 52,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,63; 29,64</t>
+          <t>3,65; 33,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,03; 44,17</t>
+          <t>8,12; 43,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,73; 21,46</t>
+          <t>3,58; 21,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,49; 36,32</t>
+          <t>4,48; 32,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,2; 49,89</t>
+          <t>10,82; 52,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,61</t>
+          <t>0,0; 42,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,47; 39,53</t>
+          <t>17,85; 39,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,73; 39,27</t>
+          <t>15,81; 39,22</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,87; 34,0</t>
+          <t>9,23; 33,53</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,07; 33,16</t>
+          <t>8,01; 35,93</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,24; 26,32</t>
+          <t>11,87; 25,43</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,75; 32,44</t>
+          <t>9,97; 32,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,78; 43,21</t>
+          <t>15,48; 43,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30,7; 66,97</t>
+          <t>31,65; 67,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30,69; 69,36</t>
+          <t>30,47; 72,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,11; 33,7</t>
+          <t>4,17; 33,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,87; 64,67</t>
+          <t>26,25; 62,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,38; 67,04</t>
+          <t>28,24; 64,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,74; 67,45</t>
+          <t>12,11; 68,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,3; 28,12</t>
+          <t>10,46; 29,26</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22,93; 45,93</t>
+          <t>23,16; 45,44</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37,16; 62,86</t>
+          <t>36,52; 62,14</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,1; 61,22</t>
+          <t>20,26; 61,14</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,87; 51,99</t>
+          <t>14,45; 49,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,11</t>
+          <t>0,0; 32,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20,72; 76,72</t>
+          <t>22,25; 76,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,93; 32,26</t>
+          <t>3,74; 33,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 72,31</t>
+          <t>0,0; 71,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,22; 69,44</t>
+          <t>8,02; 69,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,96; 86,02</t>
+          <t>15,87; 86,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,31; 49,13</t>
+          <t>10,39; 48,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15,67; 50,2</t>
+          <t>15,82; 49,51</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,95; 36,57</t>
+          <t>7,28; 39,3</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30,52; 75,06</t>
+          <t>29,66; 76,39</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,76; 33,84</t>
+          <t>9,77; 33,87</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>27,4; 59,28</t>
+          <t>27,24; 59,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,93; 32,35</t>
+          <t>8,56; 32,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22,22; 64,08</t>
+          <t>22,0; 65,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13,58; 41,31</t>
+          <t>13,62; 40,82</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,28</t>
+          <t>0,0; 29,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,64; 53,94</t>
+          <t>6,6; 53,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,09; 88,02</t>
+          <t>14,99; 87,46</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15,56; 40,6</t>
+          <t>17,64; 42,58</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21,76; 47,03</t>
+          <t>21,84; 48,28</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11,58; 33,89</t>
+          <t>11,71; 33,43</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26,25; 60,64</t>
+          <t>25,53; 63,43</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17,67; 36,9</t>
+          <t>17,94; 37,21</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>19,14; 38,27</t>
+          <t>19,22; 38,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,37; 27,31</t>
+          <t>7,46; 27,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21,28; 43,37</t>
+          <t>21,16; 44,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,42; 32,88</t>
+          <t>12,8; 32,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>18,17; 44,76</t>
+          <t>17,47; 45,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,58; 39,21</t>
+          <t>14,75; 39,78</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,3; 44,97</t>
+          <t>20,44; 45,76</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>29,76; 50,02</t>
+          <t>29,56; 50,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>21,67; 37,29</t>
+          <t>21,69; 38,06</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12,98; 29,18</t>
+          <t>12,95; 28,13</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23,75; 39,85</t>
+          <t>23,24; 40,11</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>23,96; 37,96</t>
+          <t>23,99; 38,05</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>24,26; 42,53</t>
+          <t>24,24; 42,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>19,24; 47,96</t>
+          <t>18,45; 46,97</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21,86; 52,01</t>
+          <t>21,8; 52,36</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>57,27; 82,34</t>
+          <t>56,8; 81,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>34,72; 63,5</t>
+          <t>35,51; 63,03</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,05; 54,85</t>
+          <t>18,21; 57,64</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,32; 40,11</t>
+          <t>4,47; 39,25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>46,46; 73,77</t>
+          <t>46,67; 74,5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>30,44; 46,46</t>
+          <t>30,76; 46,13</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23,18; 46,01</t>
+          <t>23,33; 45,93</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17,92; 40,94</t>
+          <t>17,67; 41,32</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>55,33; 73,54</t>
+          <t>55,76; 74,09</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>27,29; 36,11</t>
+          <t>27,44; 36,14</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>19,21; 28,57</t>
+          <t>19,51; 28,94</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>33,68; 44,25</t>
+          <t>33,63; 44,64</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>28,69; 40,75</t>
+          <t>28,56; 39,63</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>25,09; 37,85</t>
+          <t>24,95; 36,97</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>28,46; 41,47</t>
+          <t>28,64; 41,25</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>35,45; 48,95</t>
+          <t>34,33; 47,98</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>28,29; 45,54</t>
+          <t>28,62; 45,46</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>27,76; 35,01</t>
+          <t>27,74; 35,08</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24,5; 32,35</t>
+          <t>24,0; 32,52</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>35,71; 44,29</t>
+          <t>35,78; 44,41</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>31,06; 40,98</t>
+          <t>30,31; 40,89</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que se siente agotado a todas horas</t>
+          <t>Población que su trabajo le afecta de manera que se siente agotado a todas horas (tasa de respuesta: 99,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10629; 23879</t>
+          <t>10999; 24857</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6710; 19479</t>
+          <t>6307; 18416</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16488; 33094</t>
+          <t>17027; 33085</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1146; 9604</t>
+          <t>1470; 10411</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6398; 16996</t>
+          <t>6045; 17118</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11820; 22960</t>
+          <t>11739; 23084</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13878; 26038</t>
+          <t>13534; 26347</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1872; 8036</t>
+          <t>2015; 8194</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20139; 37650</t>
+          <t>19995; 37130</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21399; 38456</t>
+          <t>21543; 38277</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35408; 55023</t>
+          <t>33785; 55789</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4442; 14607</t>
+          <t>4678; 15639</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14261; 31884</t>
+          <t>13577; 30859</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11233; 26088</t>
+          <t>11744; 25884</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24862; 42994</t>
+          <t>25787; 44072</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11120; 28194</t>
+          <t>10898; 28898</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4839; 14740</t>
+          <t>5018; 15624</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3322; 14508</t>
+          <t>3784; 14346</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18876; 31833</t>
+          <t>18867; 31982</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14823; 26200</t>
+          <t>14458; 26127</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22594; 42475</t>
+          <t>23270; 43543</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18210; 36918</t>
+          <t>17814; 37168</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49545; 71857</t>
+          <t>49039; 71290</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>29905; 50566</t>
+          <t>29140; 50097</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6871; 19110</t>
+          <t>7163; 19044</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>918; 7500</t>
+          <t>924; 8424</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1707; 9388</t>
+          <t>1726; 9348</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1846; 10623</t>
+          <t>1774; 10539</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>975; 7889</t>
+          <t>973; 6966</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1829; 8948</t>
+          <t>1941; 9457</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5326</t>
+          <t>0; 5333</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8481; 18155</t>
+          <t>8200; 17979</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9174; 22912</t>
+          <t>9221; 22879</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4698; 14700</t>
+          <t>3989; 14500</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2722; 11192</t>
+          <t>2702; 12129</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11684; 25116</t>
+          <t>11330; 24267</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5687; 18920</t>
+          <t>5812; 19128</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6183; 19383</t>
+          <t>6942; 19703</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9968; 21743</t>
+          <t>10276; 21820</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12384; 27989</t>
+          <t>12296; 29175</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>933; 7652</t>
+          <t>946; 7680</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7937; 19101</t>
+          <t>7753; 18473</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8794; 20069</t>
+          <t>8455; 19360</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10276; 54403</t>
+          <t>9768; 54994</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8346; 22789</t>
+          <t>8474; 23709</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17062; 34167</t>
+          <t>17227; 33803</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23188; 39226</t>
+          <t>22786; 38778</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>23116; 74078</t>
+          <t>24516; 73981</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3414; 11933</t>
+          <t>3316; 11412</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4707</t>
+          <t>0; 4864</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3081; 11409</t>
+          <t>3309; 11424</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>671; 5510</t>
+          <t>639; 5642</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 5040</t>
+          <t>0; 5011</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>959; 8097</t>
+          <t>935; 8087</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>921; 4964</t>
+          <t>916; 4986</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1243; 5397</t>
+          <t>1142; 5315</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4688; 15023</t>
+          <t>4734; 14816</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1862; 9795</t>
+          <t>1951; 10528</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6299; 15493</t>
+          <t>6123; 15767</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3019; 9497</t>
+          <t>2742; 9505</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11454; 24786</t>
+          <t>11390; 24941</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3005; 14035</t>
+          <t>3714; 14086</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4986; 14375</t>
+          <t>4935; 14586</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4294; 13060</t>
+          <t>4305; 12904</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4268</t>
+          <t>0; 4164</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1160; 8190</t>
+          <t>1002; 8117</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1121; 6537</t>
+          <t>1114; 6496</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4701; 12269</t>
+          <t>5329; 12865</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12162; 26293</t>
+          <t>12207; 26991</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6785; 19845</t>
+          <t>6856; 19579</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7838; 18108</t>
+          <t>7622; 18940</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>10925; 22816</t>
+          <t>11094; 23006</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>16928; 33852</t>
+          <t>16999; 33751</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4011; 14866</t>
+          <t>4058; 14728</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16673; 33974</t>
+          <t>16575; 34897</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8847; 23413</t>
+          <t>9115; 23014</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7908; 19487</t>
+          <t>7606; 19824</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6761; 18185</t>
+          <t>6843; 18448</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11303; 25038</t>
+          <t>11382; 25481</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>20785; 34936</t>
+          <t>20645; 35093</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>28607; 49213</t>
+          <t>28623; 50227</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13084; 29417</t>
+          <t>13054; 28356</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>31829; 53406</t>
+          <t>31153; 53763</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>33797; 53540</t>
+          <t>33832; 53666</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>26420; 46319</t>
+          <t>26397; 45841</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>8681; 21638</t>
+          <t>8324; 21190</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8585; 20425</t>
+          <t>8563; 20564</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>32505; 46735</t>
+          <t>32241; 45974</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>17288; 31616</t>
+          <t>17680; 31380</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5034; 16193</t>
+          <t>5377; 17017</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>924; 8583</t>
+          <t>956; 8399</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>25416; 40361</t>
+          <t>25531; 40757</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>48311; 73730</t>
+          <t>48815; 73211</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>17305; 34340</t>
+          <t>17411; 34281</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>10873; 24841</t>
+          <t>10721; 25073</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>61674; 81967</t>
+          <t>62149; 82581</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>128890; 170546</t>
+          <t>129613; 170683</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>62308; 92651</t>
+          <t>63279; 93865</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>117870; 154859</t>
+          <t>117715; 156230</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>96638; 137275</t>
+          <t>96204; 133498</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>55237; 83314</t>
+          <t>54919; 81376</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>61107; 89027</t>
+          <t>61476; 88549</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>76669; 105873</t>
+          <t>74264; 103788</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>99999; 160985</t>
+          <t>101182; 160700</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>192224; 242444</t>
+          <t>192104; 242897</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>132031; 174382</t>
+          <t>129351; 175264</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>202214; 250839</t>
+          <t>202638; 251475</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>214441; 282906</t>
+          <t>209245; 282302</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P6903-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P6903-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>18,78%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>25,67; 58,02</t>
+          <t>25,21; 57,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,97; 46,63</t>
+          <t>16,57; 49,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29,07; 56,48</t>
+          <t>29,34; 56,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,11; 43,25</t>
+          <t>4,33; 32,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>21,12; 59,81</t>
+          <t>19,32; 59,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,94; 76,58</t>
+          <t>38,68; 76,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,1; 64,44</t>
+          <t>32,2; 65,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,79; 52,01</t>
+          <t>12,52; 46,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27,98; 51,96</t>
+          <t>27,98; 52,26</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30,93; 54,96</t>
+          <t>30,55; 55,51</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33,97; 56,09</t>
+          <t>34,7; 55,54</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,75; 39,27</t>
+          <t>9,84; 33,21</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>44,09%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,75; 42,62</t>
+          <t>20,44; 43,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,75; 45,74</t>
+          <t>20,55; 44,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31,15; 53,24</t>
+          <t>30,66; 52,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23,55; 62,44</t>
+          <t>24,62; 60,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,35; 47,8</t>
+          <t>14,76; 47,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,03; 41,81</t>
+          <t>9,76; 41,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,19; 74,91</t>
+          <t>44,47; 76,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,82; 57,49</t>
+          <t>33,45; 58,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22,14; 41,44</t>
+          <t>21,16; 40,11</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19,6; 40,89</t>
+          <t>20,14; 38,94</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39,08; 56,81</t>
+          <t>39,79; 58,41</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>31,77; 54,62</t>
+          <t>33,83; 54,98</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,56; 52,01</t>
+          <t>18,34; 52,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,65; 33,29</t>
+          <t>3,65; 33,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,12; 43,98</t>
+          <t>8,7; 43,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,58; 21,29</t>
+          <t>3,58; 20,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,48; 32,07</t>
+          <t>4,47; 32,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,82; 52,73</t>
+          <t>10,49; 52,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,66</t>
+          <t>0,0; 42,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,85; 39,15</t>
+          <t>17,87; 39,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,81; 39,22</t>
+          <t>16,01; 40,93</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,23; 33,53</t>
+          <t>10,89; 33,82</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,01; 35,93</t>
+          <t>8,09; 35,2</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,87; 25,43</t>
+          <t>12,28; 25,59</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>58,53%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,97; 32,8</t>
+          <t>10,7; 31,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,48; 43,92</t>
+          <t>14,02; 41,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,65; 67,21</t>
+          <t>31,88; 68,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30,47; 72,3</t>
+          <t>37,5; 74,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,17; 33,82</t>
+          <t>4,16; 36,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,25; 62,55</t>
+          <t>26,23; 62,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,24; 64,67</t>
+          <t>32,17; 66,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,11; 68,19</t>
+          <t>49,12; 73,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,46; 29,26</t>
+          <t>10,5; 29,17</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23,16; 45,44</t>
+          <t>23,52; 46,01</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36,52; 62,14</t>
+          <t>35,28; 60,81</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,26; 61,14</t>
+          <t>47,76; 69,64</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,05%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,45; 49,71</t>
+          <t>14,43; 52,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,15</t>
+          <t>0,0; 27,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22,25; 76,82</t>
+          <t>26,24; 79,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,74; 33,03</t>
+          <t>3,63; 30,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,89</t>
+          <t>0,0; 71,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,02; 69,35</t>
+          <t>8,42; 68,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,87; 86,4</t>
+          <t>16,08; 85,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,39; 48,38</t>
+          <t>12,98; 46,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15,82; 49,51</t>
+          <t>16,39; 49,48</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,28; 39,3</t>
+          <t>6,83; 36,2</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29,66; 76,39</t>
+          <t>28,13; 75,78</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,77; 33,87</t>
+          <t>10,79; 32,97</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>27,22%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>27,24; 59,65</t>
+          <t>26,75; 57,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,56; 32,47</t>
+          <t>7,17; 32,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22,0; 65,02</t>
+          <t>22,26; 64,06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13,62; 40,82</t>
+          <t>12,65; 40,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,55</t>
+          <t>0,0; 37,38</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,6; 53,46</t>
+          <t>6,67; 58,11</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,99; 87,46</t>
+          <t>14,99; 88,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17,64; 42,58</t>
+          <t>17,81; 43,8</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21,84; 48,28</t>
+          <t>21,74; 47,24</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11,71; 33,43</t>
+          <t>10,4; 32,67</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25,53; 63,43</t>
+          <t>24,57; 60,52</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17,94; 37,21</t>
+          <t>18,4; 37,24</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>31,92%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>19,22; 38,16</t>
+          <t>19,13; 38,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,46; 27,06</t>
+          <t>7,32; 28,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21,16; 44,54</t>
+          <t>21,38; 43,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,8; 32,32</t>
+          <t>15,07; 36,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>17,47; 45,53</t>
+          <t>18,81; 44,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,75; 39,78</t>
+          <t>14,46; 38,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,44; 45,76</t>
+          <t>19,56; 45,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>29,56; 50,24</t>
+          <t>30,94; 49,74</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>21,69; 38,06</t>
+          <t>20,88; 37,23</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12,95; 28,13</t>
+          <t>12,56; 28,86</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23,24; 40,11</t>
+          <t>23,84; 40,14</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>23,99; 38,05</t>
+          <t>24,87; 39,89</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>63,1%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>24,24; 42,09</t>
+          <t>24,56; 42,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>18,45; 46,97</t>
+          <t>19,85; 47,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21,8; 52,36</t>
+          <t>20,34; 50,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>56,8; 81,0</t>
+          <t>58,05; 81,02</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>35,51; 63,03</t>
+          <t>35,79; 64,04</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,21; 57,64</t>
+          <t>18,68; 58,3</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,47; 39,25</t>
+          <t>4,43; 41,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>46,67; 74,5</t>
+          <t>43,26; 66,32</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>30,76; 46,13</t>
+          <t>30,93; 46,5</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23,33; 45,93</t>
+          <t>22,64; 46,35</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17,67; 41,32</t>
+          <t>18,39; 41,74</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>55,76; 74,09</t>
+          <t>53,67; 71,22</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>39,18%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>27,44; 36,14</t>
+          <t>27,22; 35,99</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>19,51; 28,94</t>
+          <t>19,38; 28,66</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>33,63; 44,64</t>
+          <t>33,49; 44,56</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>28,56; 39,63</t>
+          <t>30,58; 41,94</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>24,95; 36,97</t>
+          <t>25,12; 37,58</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>28,64; 41,25</t>
+          <t>27,66; 41,32</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,33; 47,98</t>
+          <t>34,78; 48,52</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>28,62; 45,46</t>
+          <t>37,93; 47,13</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>27,74; 35,08</t>
+          <t>27,72; 34,98</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24,0; 32,52</t>
+          <t>24,38; 32,36</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>35,78; 44,41</t>
+          <t>35,89; 44,44</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>30,31; 40,89</t>
+          <t>35,34; 42,83</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4595</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4340</t>
+          <t>4116</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8936</t>
+          <t>7967</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10999; 24857</t>
+          <t>10801; 24513</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6307; 18416</t>
+          <t>6546; 19546</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17027; 33085</t>
+          <t>17186; 33261</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1470; 10411</t>
+          <t>1136; 8543</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6045; 17118</t>
+          <t>5530; 16993</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11739; 23084</t>
+          <t>11661; 23202</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13534; 26347</t>
+          <t>13163; 26810</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2015; 8194</t>
+          <t>2029; 7475</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19995; 37130</t>
+          <t>19996; 37345</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21543; 38277</t>
+          <t>21276; 38657</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>33785; 55789</t>
+          <t>34508; 55239</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4678; 15639</t>
+          <t>4175; 14088</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18973</t>
+          <t>20249</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>20327</t>
+          <t>21421</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>39300</t>
+          <t>41670</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13577; 30859</t>
+          <t>14798; 31744</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11744; 25884</t>
+          <t>11632; 25462</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25787; 44072</t>
+          <t>25383; 43508</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10898; 28898</t>
+          <t>11817; 28943</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5018; 15624</t>
+          <t>4826; 15430</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3784; 14346</t>
+          <t>3349; 14110</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18867; 31982</t>
+          <t>18989; 32532</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14458; 26127</t>
+          <t>15557; 27347</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23270; 43543</t>
+          <t>22238; 42146</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17814; 37168</t>
+          <t>18312; 35396</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49039; 71290</t>
+          <t>49930; 73290</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>29140; 50097</t>
+          <t>31975; 51966</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5160</t>
+          <t>5124</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12496</t>
+          <t>12640</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17657</t>
+          <t>17765</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7163; 19044</t>
+          <t>6715; 19153</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>924; 8424</t>
+          <t>924; 8520</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1726; 9348</t>
+          <t>1850; 9294</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1774; 10539</t>
+          <t>1774; 10188</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>973; 6966</t>
+          <t>971; 7148</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1941; 9457</t>
+          <t>1881; 9501</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5333</t>
+          <t>0; 5252</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8200; 17979</t>
+          <t>8395; 18314</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9221; 22879</t>
+          <t>9337; 23876</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3989; 14500</t>
+          <t>4710; 14623</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2702; 12129</t>
+          <t>2729; 11882</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11330; 24267</t>
+          <t>11861; 24706</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20511</t>
+          <t>29925</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>29847</t>
+          <t>32964</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>50358</t>
+          <t>62889</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5812; 19128</t>
+          <t>6242; 18559</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6942; 19703</t>
+          <t>6289; 18530</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10276; 21820</t>
+          <t>10349; 22146</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12296; 29175</t>
+          <t>20315; 40353</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>946; 7680</t>
+          <t>945; 8260</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7753; 18473</t>
+          <t>7746; 18456</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8455; 19360</t>
+          <t>9631; 19936</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9768; 54994</t>
+          <t>26173; 39075</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8474; 23709</t>
+          <t>8507; 23634</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17227; 33803</t>
+          <t>17500; 34228</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22786; 38778</t>
+          <t>22017; 37943</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>24516; 73981</t>
+          <t>51314; 74827</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t>2875</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>3700</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5509</t>
+          <t>6575</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3316; 11412</t>
+          <t>3313; 11970</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4864</t>
+          <t>0; 4208</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3309; 11424</t>
+          <t>3902; 11796</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>639; 5642</t>
+          <t>760; 6382</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 5011</t>
+          <t>0; 5018</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>935; 8087</t>
+          <t>982; 8035</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>916; 4986</t>
+          <t>928; 4933</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1142; 5315</t>
+          <t>1764; 6332</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4734; 14816</t>
+          <t>4904; 14807</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1951; 10528</t>
+          <t>1830; 9698</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6123; 15767</t>
+          <t>5807; 15641</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2742; 9505</t>
+          <t>3726; 11379</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7965</t>
+          <t>8457</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>8412</t>
+          <t>8817</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>16377</t>
+          <t>17274</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11390; 24941</t>
+          <t>11183; 24176</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3714; 14086</t>
+          <t>3110; 14231</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4935; 14586</t>
+          <t>4995; 14371</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4305; 12904</t>
+          <t>4158; 13465</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4164</t>
+          <t>0; 5269</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1002; 8117</t>
+          <t>1013; 8823</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1114; 6496</t>
+          <t>1114; 6576</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5329; 12865</t>
+          <t>5445; 13396</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12207; 26991</t>
+          <t>12154; 26410</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6856; 19579</t>
+          <t>6088; 19134</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7622; 18940</t>
+          <t>7336; 18071</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>11094; 23006</t>
+          <t>11672; 23630</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15320</t>
+          <t>20265</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>27472</t>
+          <t>32001</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>42792</t>
+          <t>52266</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>16999; 33751</t>
+          <t>16916; 34479</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4058; 14728</t>
+          <t>3983; 15243</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16575; 34897</t>
+          <t>16750; 33685</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9115; 23014</t>
+          <t>12619; 30967</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7606; 19824</t>
+          <t>8188; 19344</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6843; 18448</t>
+          <t>6705; 17959</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11382; 25481</t>
+          <t>10893; 25062</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>20645; 35093</t>
+          <t>24759; 39800</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>28623; 50227</t>
+          <t>27557; 49137</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13054; 28356</t>
+          <t>12661; 29092</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>31153; 53763</t>
+          <t>31949; 53801</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>33832; 53666</t>
+          <t>40723; 65317</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>40077</t>
+          <t>46962</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>32393</t>
+          <t>31372</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>72470</t>
+          <t>78334</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>26397; 45841</t>
+          <t>26745; 46416</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>8324; 21190</t>
+          <t>8956; 21296</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8563; 20564</t>
+          <t>7988; 20003</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>32241; 45974</t>
+          <t>38696; 54006</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>17680; 31380</t>
+          <t>17817; 31881</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5377; 17017</t>
+          <t>5515; 17211</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>956; 8399</t>
+          <t>948; 8953</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>25531; 40757</t>
+          <t>24864; 38120</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>48815; 73211</t>
+          <t>49087; 73795</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>17411; 34281</t>
+          <t>16898; 34595</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>10721; 25073</t>
+          <t>11156; 25326</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>62149; 82581</t>
+          <t>66630; 88415</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>115185</t>
+          <t>137708</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>138214</t>
+          <t>147031</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>253399</t>
+          <t>284739</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>129613; 170683</t>
+          <t>128558; 169966</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>63279; 93865</t>
+          <t>62856; 92954</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>117715; 156230</t>
+          <t>117232; 155947</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>96204; 133498</t>
+          <t>116852; 160285</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>54919; 81376</t>
+          <t>55287; 82728</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>61476; 88549</t>
+          <t>59371; 88706</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>74264; 103788</t>
+          <t>75223; 104953</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>101182; 160700</t>
+          <t>130709; 162433</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>192104; 242897</t>
+          <t>191958; 242244</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>129351; 175264</t>
+          <t>131419; 174395</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>202638; 251475</t>
+          <t>203259; 251646</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>209245; 282302</t>
+          <t>256828; 311246</t>
         </is>
       </c>
     </row>
